--- a/seed_data/excel/Financial_Model_2026.xlsx
+++ b/seed_data/excel/Financial_Model_2026.xlsx
@@ -29,6 +29,7 @@
     <definedName function="false" hidden="false" name="Inputs_DemoToday" vbProcedure="false">Inputs!$B$12</definedName>
     <definedName function="false" hidden="false" name="Inputs_Margin" vbProcedure="false">Inputs!$B$7</definedName>
     <definedName function="false" hidden="false" name="Inputs_TotalDebt" vbProcedure="false">Inputs!$B$4</definedName>
+    <definedName function="false" hidden="false" name="Ledger_DemoToday" vbProcedure="false">_meta!$B$4</definedName>
     <definedName function="false" hidden="false" name="Outstanding_DemoToday" vbProcedure="false">Debt!$H$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -280,7 +281,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25T08:51:04+00:00</t>
+    <t xml:space="preserve">2026-10-05T19:07:43+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -373,20 +374,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -410,295 +407,295 @@
   <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="0" t="n">
         <v>72000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="0" t="n">
         <v>21600000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="0" t="n">
         <v>50400000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="0" t="n">
         <v>20400000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="0" t="n">
         <v>30000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="0" t="n">
         <v>3.25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="0" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="0" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="0" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="1" t="n">
         <v>44515</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="1" t="n">
         <v>46280</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="0" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="0" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="1" t="n">
         <v>45731</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="0" t="n">
         <v>-0.5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="0" t="n">
         <v>2022</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="0" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="0" t="n">
         <v>2023</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="0" t="n">
         <v>3.6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="0" t="n">
         <v>2024</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="0" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="0" t="n">
         <v>2025</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="0" t="n">
         <v>2.4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="0" t="n">
         <v>2026</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="0" t="n">
         <v>2.1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="0" t="n">
         <v>2027</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="0" t="n">
         <v>2028</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="0" t="n">
         <v>2029</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="0" t="n">
         <v>2030</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="0" t="n">
         <v>2031</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="0" t="n">
         <v>2032</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="0" t="n">
         <v>2033</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="0" t="n">
         <v>2034</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="0" t="n">
         <v>2035</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44545</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="0" t="n">
         <v>15000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="0" t="n">
         <v>15000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44910</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="0" t="n">
         <v>12000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="0" t="n">
         <v>8400000</v>
       </c>
     </row>
@@ -721,870 +718,870 @@
   <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>44561</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="n">
+      <c r="C2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>15000000</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="E2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B2),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>2.75</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="0" t="n">
         <f aca="false">ROUND(C2*F2/100/2,2)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="0" t="n">
         <f aca="false">C2+D2-E2</f>
         <v>15000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="0" t="n">
         <f aca="false">H2</f>
         <v>15000000</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="0" t="n">
         <v>15000000</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B3),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>4</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="0" t="n">
         <f aca="false">ROUND(C3*F3/100/2,2)</f>
         <v>300000</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="0" t="n">
         <f aca="false">C3+D3-E3</f>
         <v>30000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="0" t="n">
         <f aca="false">H3</f>
         <v>30000000</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="0" t="n">
         <v>12000000</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B4),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>4</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="0" t="n">
         <f aca="false">ROUND(C4*F4/100/2,2)</f>
         <v>600000</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="0" t="n">
         <f aca="false">C4+D4-E4</f>
         <v>42000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="0" t="n">
         <f aca="false">H4</f>
         <v>42000000</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>8400000</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B5),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>6.85</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="0" t="n">
         <f aca="false">ROUND(C5*F5/100/2,2)</f>
         <v>1438500</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="0" t="n">
         <f aca="false">C5+D5-E5</f>
         <v>50400000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>45291</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="0" t="n">
         <f aca="false">H5</f>
         <v>50400000</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="n">
+      <c r="D6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B6),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>6.85</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="0" t="n">
         <f aca="false">ROUND(C6*F6/100/2,2)</f>
         <v>1726200</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="0" t="n">
         <f aca="false">C6+D6-E6</f>
         <v>50400000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="0" t="n">
         <f aca="false">H6</f>
         <v>50400000</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1" t="n">
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
         <v>1000000</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B7),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>6.75</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="0" t="n">
         <f aca="false">ROUND(C7*F7/100/2,2)</f>
         <v>1701000</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="0" t="n">
         <f aca="false">C7+D7-E7</f>
         <v>49400000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="0" t="n">
         <f aca="false">H7</f>
         <v>49400000</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1" t="n">
+      <c r="D8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0" t="n">
         <v>1100000</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B8),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>6.75</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="0" t="n">
         <f aca="false">ROUND(C8*F8/100/2,2)</f>
         <v>1667250</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="0" t="n">
         <f aca="false">C8+D8-E8</f>
         <v>48300000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="0" t="n">
         <f aca="false">H8</f>
         <v>48300000</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1" t="n">
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="n">
         <v>1300000</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B9),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.65</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="0" t="n">
         <f aca="false">ROUND(C9*F9/100/2,2)</f>
         <v>1364475</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="0" t="n">
         <f aca="false">C9+D9-E9</f>
         <v>47000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="0" t="n">
         <f aca="false">H9</f>
         <v>47000000</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1" t="n">
+      <c r="D10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0" t="n">
         <v>1400000</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B10),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.65</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="0" t="n">
         <f aca="false">ROUND(C10*F10/100/2,2)</f>
         <v>1327750</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="0" t="n">
         <f aca="false">C10+D10-E10</f>
         <v>45600000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="0" t="n">
         <f aca="false">H10</f>
         <v>45600000</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1" t="n">
+      <c r="D11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="n">
         <v>1500000</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B11),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.35</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="0" t="n">
         <f aca="false">ROUND(C11*F11/100/2,2)</f>
         <v>1219800</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="0" t="n">
         <f aca="false">C11+D11-E11</f>
         <v>44100000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="0" t="n">
         <f aca="false">H11</f>
         <v>44100000</v>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1" t="n">
+      <c r="D12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0" t="n">
         <v>1600000</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B12),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.35</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="0" t="n">
         <f aca="false">ROUND(C12*F12/100/2,2)</f>
         <v>1179675</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="0" t="n">
         <f aca="false">C12+D12-E12</f>
         <v>42500000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="1" t="n">
         <v>46568</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="0" t="n">
         <f aca="false">H12</f>
         <v>42500000</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1" t="n">
+      <c r="D13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <v>1700000</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B13),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="0" t="n">
         <f aca="false">ROUND(C13*F13/100/2,2)</f>
         <v>1115625</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="0" t="n">
         <f aca="false">C13+D13-E13</f>
         <v>40800000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="1" t="n">
         <v>46752</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="0" t="n">
         <f aca="false">H13</f>
         <v>40800000</v>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1" t="n">
+      <c r="D14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <v>1800000</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B14),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="G14" s="0" t="n">
         <f aca="false">ROUND(C14*F14/100/2,2)</f>
         <v>1071000</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="0" t="n">
         <f aca="false">C14+D14-E14</f>
         <v>39000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="1" t="n">
         <v>46934</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="0" t="n">
         <f aca="false">H14</f>
         <v>39000000</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1" t="n">
+      <c r="D15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0" t="n">
         <v>1900000</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B15),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="0" t="n">
         <f aca="false">ROUND(C15*F15/100/2,2)</f>
         <v>1023750</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="0" t="n">
         <f aca="false">C15+D15-E15</f>
         <v>37100000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="1" t="n">
         <v>47118</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="0" t="n">
         <f aca="false">H15</f>
         <v>37100000</v>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1" t="n">
+      <c r="D16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0" t="n">
         <v>2000000</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B16),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="0" t="n">
         <f aca="false">ROUND(C16*F16/100/2,2)</f>
         <v>973875</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="0" t="n">
         <f aca="false">C16+D16-E16</f>
         <v>35100000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="1" t="n">
         <v>47299</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="0" t="n">
         <f aca="false">H16</f>
         <v>35100000</v>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1" t="n">
+      <c r="D17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0" t="n">
         <v>2100000</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B17),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="0" t="n">
         <f aca="false">ROUND(C17*F17/100/2,2)</f>
         <v>921375</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="0" t="n">
         <f aca="false">C17+D17-E17</f>
         <v>33000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="1" t="n">
         <v>47483</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="0" t="n">
         <f aca="false">H17</f>
         <v>33000000</v>
       </c>
-      <c r="D18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1" t="n">
+      <c r="D18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0" t="n">
         <v>2200000</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B18),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="G18" s="0" t="n">
         <f aca="false">ROUND(C18*F18/100/2,2)</f>
         <v>866250</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="0" t="n">
         <f aca="false">C18+D18-E18</f>
         <v>30800000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="1" t="n">
         <v>47664</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="0" t="n">
         <f aca="false">H18</f>
         <v>30800000</v>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1" t="n">
+      <c r="D19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="0" t="n">
         <v>2300000</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B19),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="0" t="n">
         <f aca="false">ROUND(C19*F19/100/2,2)</f>
         <v>808500</v>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="H19" s="0" t="n">
         <f aca="false">C19+D19-E19</f>
         <v>28500000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="1" t="n">
         <v>47848</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="0" t="n">
         <f aca="false">H19</f>
         <v>28500000</v>
       </c>
-      <c r="D20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1" t="n">
+      <c r="D20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="0" t="n">
         <v>2400000</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B20),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="G20" s="0" t="n">
         <f aca="false">ROUND(C20*F20/100/2,2)</f>
         <v>748125</v>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="H20" s="0" t="n">
         <f aca="false">C20+D20-E20</f>
         <v>26100000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="1" t="n">
         <v>48029</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="0" t="n">
         <f aca="false">H20</f>
         <v>26100000</v>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1" t="n">
+      <c r="D21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="0" t="n">
         <v>2500000</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="F21" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B21),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G21" s="1" t="n">
+      <c r="G21" s="0" t="n">
         <f aca="false">ROUND(C21*F21/100/2,2)</f>
         <v>685125</v>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="H21" s="0" t="n">
         <f aca="false">C21+D21-E21</f>
         <v>23600000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="1" t="n">
         <v>48213</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="0" t="n">
         <f aca="false">H21</f>
         <v>23600000</v>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="1" t="n">
+      <c r="D22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="0" t="n">
         <v>2600000</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="F22" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B22),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G22" s="1" t="n">
+      <c r="G22" s="0" t="n">
         <f aca="false">ROUND(C22*F22/100/2,2)</f>
         <v>619500</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="0" t="n">
         <f aca="false">C22+D22-E22</f>
         <v>21000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="1" t="n">
         <v>48395</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="0" t="n">
         <f aca="false">H22</f>
         <v>21000000</v>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1" t="n">
+      <c r="D23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0" t="n">
         <v>2700000</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="F23" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B23),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G23" s="1" t="n">
+      <c r="G23" s="0" t="n">
         <f aca="false">ROUND(C23*F23/100/2,2)</f>
         <v>551250</v>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="H23" s="0" t="n">
         <f aca="false">C23+D23-E23</f>
         <v>18300000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="1" t="n">
         <v>48579</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="0" t="n">
         <f aca="false">H23</f>
         <v>18300000</v>
       </c>
-      <c r="D24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="1" t="n">
+      <c r="D24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0" t="n">
         <v>2800000</v>
       </c>
-      <c r="F24" s="1" t="n">
+      <c r="F24" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B24),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G24" s="1" t="n">
+      <c r="G24" s="0" t="n">
         <f aca="false">ROUND(C24*F24/100/2,2)</f>
         <v>480375</v>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="H24" s="0" t="n">
         <f aca="false">C24+D24-E24</f>
         <v>15500000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="1" t="n">
         <v>48760</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="0" t="n">
         <f aca="false">H24</f>
         <v>15500000</v>
       </c>
-      <c r="D25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1" t="n">
+      <c r="D25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0" t="n">
         <v>2900000</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="F25" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B25),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G25" s="1" t="n">
+      <c r="G25" s="0" t="n">
         <f aca="false">ROUND(C25*F25/100/2,2)</f>
         <v>406875</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="H25" s="0" t="n">
         <f aca="false">C25+D25-E25</f>
         <v>12600000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="1" t="n">
         <v>48944</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="0" t="n">
         <f aca="false">H25</f>
         <v>12600000</v>
       </c>
-      <c r="D26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1" t="n">
+      <c r="D26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0" t="n">
         <v>3000000</v>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="F26" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B26),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G26" s="1" t="n">
+      <c r="G26" s="0" t="n">
         <f aca="false">ROUND(C26*F26/100/2,2)</f>
         <v>330750</v>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="H26" s="0" t="n">
         <f aca="false">C26+D26-E26</f>
         <v>9600000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" s="1" t="n">
         <v>49125</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="0" t="n">
         <f aca="false">H26</f>
         <v>9600000</v>
       </c>
-      <c r="D27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1" t="n">
+      <c r="D27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="0" t="n">
         <v>3100000</v>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="F27" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B27),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G27" s="1" t="n">
+      <c r="G27" s="0" t="n">
         <f aca="false">ROUND(C27*F27/100/2,2)</f>
         <v>252000</v>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H27" s="0" t="n">
         <f aca="false">C27+D27-E27</f>
         <v>6500000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="1" t="n">
         <v>49309</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="0" t="n">
         <f aca="false">H27</f>
         <v>6500000</v>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1" t="n">
+      <c r="D28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="0" t="n">
         <v>3200000</v>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="F28" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B28),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G28" s="1" t="n">
+      <c r="G28" s="0" t="n">
         <f aca="false">ROUND(C28*F28/100/2,2)</f>
         <v>170625</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="0" t="n">
         <f aca="false">C28+D28-E28</f>
         <v>3300000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="1" t="n">
         <v>49490</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="0" t="n">
         <f aca="false">H28</f>
         <v>3300000</v>
       </c>
-      <c r="D29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1" t="n">
+      <c r="D29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="0" t="n">
         <v>3300000</v>
       </c>
-      <c r="F29" s="1" t="n">
+      <c r="F29" s="0" t="n">
         <f aca="false">VLOOKUP(YEAR(B29),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
         <v>5.25</v>
       </c>
-      <c r="G29" s="1" t="n">
+      <c r="G29" s="0" t="n">
         <f aca="false">ROUND(C29*F29/100/2,2)</f>
         <v>86625</v>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="H29" s="0" t="n">
         <f aca="false">C29+D29-E29</f>
         <v>0</v>
       </c>
@@ -1608,361 +1605,361 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>45291</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="0" t="n">
         <v>1225600</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C2,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C2,Debt!$A$2:$A$29,0)))/2</f>
         <v>863100</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="0" t="n">
         <f aca="false">ROUND(D2/E2,2)</f>
         <v>1.42</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="0" t="n">
         <f aca="false">IF(B2&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.25</v>
       </c>
-      <c r="H2" s="1" t="str">
+      <c r="H2" s="0" t="str">
         <f aca="false">IF(F2&gt;=G2,"pass","fail")</f>
         <v>pass</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="0" t="n">
         <v>1863700</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C3,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C3,Debt!$A$2:$A$29,0)))/2</f>
         <v>1350500</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="0" t="n">
         <f aca="false">ROUND(D3/E3,2)</f>
         <v>1.38</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="0" t="n">
         <f aca="false">IF(B3&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.25</v>
       </c>
-      <c r="H3" s="1" t="str">
+      <c r="H3" s="0" t="str">
         <f aca="false">IF(F3&gt;=G3,"pass","fail")</f>
         <v>pass</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="0" t="n">
         <v>1769200</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C4,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C4,Debt!$A$2:$A$29,0)))/2</f>
         <v>1350500</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="0" t="n">
         <f aca="false">ROUND(D4/E4,2)</f>
         <v>1.31</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="0" t="n">
         <f aca="false">IF(B4&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.25</v>
       </c>
-      <c r="H4" s="1" t="str">
+      <c r="H4" s="0" t="str">
         <f aca="false">IF(F4&gt;=G4,"pass","fail")</f>
         <v>pass</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1757200</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C5,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C5,Debt!$A$2:$A$29,0)))/2</f>
         <v>1383625</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="0" t="n">
         <f aca="false">ROUND(D5/E5,2)</f>
         <v>1.27</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="0" t="n">
         <f aca="false">IF(B5&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.25</v>
       </c>
-      <c r="H5" s="1" t="str">
+      <c r="H5" s="0" t="str">
         <f aca="false">IF(F5&gt;=G5,"pass","fail")</f>
         <v>pass</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1715700</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C6,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C6,Debt!$A$2:$A$29,0)))/2</f>
         <v>1383625</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="0" t="n">
         <f aca="false">ROUND(D6/E6,2)</f>
         <v>1.24</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="0" t="n">
         <f aca="false">IF(B6&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.25</v>
       </c>
-      <c r="H6" s="1" t="str">
+      <c r="H6" s="0" t="str">
         <f aca="false">IF(F6&gt;=G6,"pass","fail")</f>
         <v>fail</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1638700</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C7,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C7,Debt!$A$2:$A$29,0)))/2</f>
         <v>1332237.5</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="0" t="n">
         <f aca="false">ROUND(D7/E7,2)</f>
         <v>1.23</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="0" t="n">
         <f aca="false">IF(B7&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.2</v>
       </c>
-      <c r="H7" s="1" t="str">
+      <c r="H7" s="0" t="str">
         <f aca="false">IF(F7&gt;=G7,"pass","fail")</f>
         <v>pass</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <v>1718600</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C8,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C8,Debt!$A$2:$A$29,0)))/2</f>
         <v>1332237.5</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="0" t="n">
         <f aca="false">ROUND(D8/E8,2)</f>
         <v>1.29</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="0" t="n">
         <f aca="false">IF(B8&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.2</v>
       </c>
-      <c r="H8" s="1" t="str">
+      <c r="H8" s="0" t="str">
         <f aca="false">IF(F8&gt;=G8,"pass","fail")</f>
         <v>pass</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="0" t="n">
         <v>1814000</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C9,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C9,Debt!$A$2:$A$29,0)))/2</f>
         <v>1363875</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="0" t="n">
         <f aca="false">ROUND(D9/E9,2)</f>
         <v>1.33</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="0" t="n">
         <f aca="false">IF(B9&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.2</v>
       </c>
-      <c r="H9" s="1" t="str">
+      <c r="H9" s="0" t="str">
         <f aca="false">IF(F9&gt;=G9,"pass","fail")</f>
         <v>pass</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1854900</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C10,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C10,Debt!$A$2:$A$29,0)))/2</f>
         <v>1363875</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="0" t="n">
         <f aca="false">ROUND(D10/E10,2)</f>
         <v>1.36</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="0" t="n">
         <f aca="false">IF(B10&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.2</v>
       </c>
-      <c r="H10" s="1" t="str">
+      <c r="H10" s="0" t="str">
         <f aca="false">IF(F10&gt;=G10,"pass","fail")</f>
         <v>pass</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="0" t="n">
         <v>1822300</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C11,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C11,Debt!$A$2:$A$29,0)))/2</f>
         <v>1359900</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="0" t="n">
         <f aca="false">ROUND(D11/E11,2)</f>
         <v>1.34</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="0" t="n">
         <f aca="false">IF(B11&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.2</v>
       </c>
-      <c r="H11" s="1" t="str">
+      <c r="H11" s="0" t="str">
         <f aca="false">IF(F11&gt;=G11,"pass","fail")</f>
         <v>pass</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>1863100</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="0" t="n">
         <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C12,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C12,Debt!$A$2:$A$29,0)))/2</f>
         <v>1359900</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="0" t="n">
         <f aca="false">ROUND(D12/E12,2)</f>
         <v>1.37</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="0" t="n">
         <f aca="false">IF(B12&gt;=Inputs!$B$15,Inputs!$B$14,Inputs!$B$13)</f>
         <v>1.2</v>
       </c>
-      <c r="H12" s="1" t="str">
+      <c r="H12" s="0" t="str">
         <f aca="false">IF(F12&gt;=G12,"pass","fail")</f>
         <v>pass</v>
       </c>
@@ -1986,253 +1983,253 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="0" t="n">
         <f aca="false">DSCR!D2</f>
         <v>1225600</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="0" t="n">
         <f aca="false">DSCR!E2</f>
         <v>863100</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="0" t="n">
         <f aca="false">B2-C2</f>
         <v>362500</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="0" t="n">
         <f aca="false">D2</f>
         <v>362500</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="0" t="n">
         <f aca="false">DSCR!D3</f>
         <v>1863700</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="0" t="n">
         <f aca="false">DSCR!E3</f>
         <v>1350500</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="0" t="n">
         <f aca="false">B3-C3</f>
         <v>513200</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="0" t="n">
         <f aca="false">E2+D3</f>
         <v>875700</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="0" t="n">
         <f aca="false">DSCR!D4</f>
         <v>1769200</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="0" t="n">
         <f aca="false">DSCR!E4</f>
         <v>1350500</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="0" t="n">
         <f aca="false">B4-C4</f>
         <v>418700</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="0" t="n">
         <f aca="false">E3+D4</f>
         <v>1294400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="0" t="n">
         <f aca="false">DSCR!D5</f>
         <v>1757200</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="0" t="n">
         <f aca="false">DSCR!E5</f>
         <v>1383625</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <f aca="false">B5-C5</f>
         <v>373575</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="0" t="n">
         <f aca="false">E4+D5</f>
         <v>1667975</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="0" t="n">
         <f aca="false">DSCR!D6</f>
         <v>1715700</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="0" t="n">
         <f aca="false">DSCR!E6</f>
         <v>1383625</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <f aca="false">B6-C6</f>
         <v>332075</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="0" t="n">
         <f aca="false">E5+D6</f>
         <v>2000050</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="0" t="n">
         <f aca="false">DSCR!D7</f>
         <v>1638700</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="0" t="n">
         <f aca="false">DSCR!E7</f>
         <v>1332237.5</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <f aca="false">B7-C7</f>
         <v>306462.5</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="0" t="n">
         <f aca="false">E6+D7</f>
         <v>2306512.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="0" t="n">
         <f aca="false">DSCR!D8</f>
         <v>1718600</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="0" t="n">
         <f aca="false">DSCR!E8</f>
         <v>1332237.5</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">B8-C8</f>
         <v>386362.5</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="0" t="n">
         <f aca="false">E7+D8</f>
         <v>2692875</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="0" t="n">
         <f aca="false">DSCR!D9</f>
         <v>1814000</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="0" t="n">
         <f aca="false">DSCR!E9</f>
         <v>1363875</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="0" t="n">
         <f aca="false">B9-C9</f>
         <v>450125</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="0" t="n">
         <f aca="false">E8+D9</f>
         <v>3143000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="0" t="n">
         <f aca="false">DSCR!D10</f>
         <v>1854900</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="0" t="n">
         <f aca="false">DSCR!E10</f>
         <v>1363875</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <f aca="false">B10-C10</f>
         <v>491025</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="0" t="n">
         <f aca="false">E9+D10</f>
         <v>3634025</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="0" t="n">
         <f aca="false">DSCR!D11</f>
         <v>1822300</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="0" t="n">
         <f aca="false">DSCR!E11</f>
         <v>1359900</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="0" t="n">
         <f aca="false">B11-C11</f>
         <v>462400</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="0" t="n">
         <f aca="false">E10+D11</f>
         <v>4096425</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="0" t="n">
         <f aca="false">DSCR!D12</f>
         <v>1863100</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="0" t="n">
         <f aca="false">DSCR!E12</f>
         <v>1359900</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <f aca="false">B12-C12</f>
         <v>503200</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="0" t="n">
         <f aca="false">E11+D12</f>
         <v>4599625</v>
       </c>
@@ -2257,31 +2254,31 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="0" t="s">
         <v>82</v>
       </c>
     </row>

--- a/seed_data/excel/Financial_Model_2026.xlsx
+++ b/seed_data/excel/Financial_Model_2026.xlsx
@@ -30,7 +30,7 @@
     <definedName function="false" hidden="false" name="Inputs_Margin" vbProcedure="false">Inputs!$B$7</definedName>
     <definedName function="false" hidden="false" name="Inputs_TotalDebt" vbProcedure="false">Inputs!$B$4</definedName>
     <definedName function="false" hidden="false" name="Ledger_DemoToday" vbProcedure="false">_meta!$B$4</definedName>
-    <definedName function="false" hidden="false" name="Outstanding_DemoToday" vbProcedure="false">Debt!$H$11</definedName>
+    <definedName function="false" hidden="false" name="Outstanding_DemoToday" vbProcedure="false">Debt!$H$9</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -42,30 +42,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="80">
   <si>
     <t xml:space="preserve">Project</t>
   </si>
   <si>
-    <t xml:space="preserve">Ankara RES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capex (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total debt (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local bank debt (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECA debt (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margin over base (%)</t>
+    <t xml:space="preserve">Karatepe RES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capex (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total debt (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local bank debt (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECA debt (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin over base, current (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Grace (months)</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">Year</t>
   </si>
   <si>
-    <t xml:space="preserve">Base rate % (EURIBOR 6M, fictional)</t>
+    <t xml:space="preserve">Base rate % (Term SOFR 6M, fictional)</t>
   </si>
   <si>
     <t xml:space="preserve">Drawdown date</t>
   </si>
   <si>
-    <t xml:space="preserve">Amount (EUR)</t>
+    <t xml:space="preserve">Amount (USD)</t>
   </si>
   <si>
     <t xml:space="preserve">Period</t>
@@ -110,28 +110,22 @@
     <t xml:space="preserve">End date</t>
   </si>
   <si>
-    <t xml:space="preserve">Opening (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drawdown (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal (EUR)</t>
+    <t xml:space="preserve">Opening (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawdown (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal (USD)</t>
   </si>
   <si>
     <t xml:space="preserve">All-in rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">Interest (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2_2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H1_2022</t>
+    <t xml:space="preserve">Interest (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closing (USD)</t>
   </si>
   <si>
     <t xml:space="preserve">H2_2022</t>
@@ -209,9 +203,6 @@
     <t xml:space="preserve">H2_2034</t>
   </si>
   <si>
-    <t xml:space="preserve">H1_2035</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quarter</t>
   </si>
   <si>
@@ -221,10 +212,10 @@
     <t xml:space="preserve">Half</t>
   </si>
   <si>
-    <t xml:space="preserve">CFADS (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt service (EUR)</t>
+    <t xml:space="preserve">CFADS (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt service (USD)</t>
   </si>
   <si>
     <t xml:space="preserve">DSCR</t>
@@ -269,10 +260,10 @@
     <t xml:space="preserve">Q2_2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Cash to equity (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative (EUR)</t>
+    <t xml:space="preserve">Cash to equity (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative (USD)</t>
   </si>
   <si>
     <t xml:space="preserve">DEMO — synthetic demo workbook (Company AI V0); figures are fictional</t>
@@ -281,7 +272,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-05T19:07:43+00:00</t>
+    <t xml:space="preserve">2026-10-09T22:07:38+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -404,7 +395,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -424,7 +415,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>72000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -432,7 +423,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>21600000</v>
+        <v>6400000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -440,7 +431,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>50400000</v>
+        <v>13600000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -448,7 +439,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>20400000</v>
+        <v>13600000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -456,7 +447,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>30000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -464,7 +455,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -472,7 +463,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -480,7 +471,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -488,7 +479,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -496,7 +487,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44515</v>
+        <v>44525</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -541,162 +532,138 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>-0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.75</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B25" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B26" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B28" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B32" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>19</v>
+      <c r="A34" s="1" t="n">
+        <v>44757</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>8000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
-        <v>44545</v>
+        <v>44941</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>15000000</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
-        <v>44742</v>
-      </c>
-      <c r="B36" s="0" t="n">
-        <v>15000000</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>44910</v>
-      </c>
-      <c r="B37" s="0" t="n">
-        <v>12000000</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>45107</v>
-      </c>
-      <c r="B38" s="0" t="n">
-        <v>8400000</v>
+        <v>5600000</v>
       </c>
     </row>
   </sheetData>
@@ -715,7 +682,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16"/>
@@ -752,20 +719,20 @@
         <v>28</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44561</v>
+        <v>44926</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>15000000</v>
+        <v>8000000</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B2),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>2.75</v>
+        <f aca="false">VLOOKUP(YEAR(B2),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>4.9</v>
       </c>
       <c r="G2" s="0" t="n">
         <f aca="false">ROUND(C2*F2/100/2,2)</f>
@@ -773,7 +740,7 @@
       </c>
       <c r="H2" s="0" t="n">
         <f aca="false">C2+D2-E2</f>
-        <v>15000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -781,29 +748,29 @@
         <v>29</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="C3" s="0" t="n">
         <f aca="false">H2</f>
-        <v>15000000</v>
+        <v>8000000</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>15000000</v>
+        <v>5600000</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0</v>
+        <v>172700</v>
       </c>
       <c r="F3" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B3),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>4</v>
+        <f aca="false">VLOOKUP(YEAR(B3),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>7.7</v>
       </c>
       <c r="G3" s="0" t="n">
         <f aca="false">ROUND(C3*F3/100/2,2)</f>
-        <v>300000</v>
+        <v>308000</v>
       </c>
       <c r="H3" s="0" t="n">
         <f aca="false">C3+D3-E3</f>
-        <v>30000000</v>
+        <v>13427300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -811,29 +778,29 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="C4" s="0" t="n">
         <f aca="false">H3</f>
-        <v>30000000</v>
+        <v>13427300</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>12000000</v>
+        <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0</v>
+        <v>206900</v>
       </c>
       <c r="F4" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B4),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>4</v>
+        <f aca="false">VLOOKUP(YEAR(B4),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>7.7</v>
       </c>
       <c r="G4" s="0" t="n">
         <f aca="false">ROUND(C4*F4/100/2,2)</f>
-        <v>600000</v>
+        <v>516951.05</v>
       </c>
       <c r="H4" s="0" t="n">
         <f aca="false">C4+D4-E4</f>
-        <v>42000000</v>
+        <v>13220400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -841,29 +808,29 @@
         <v>31</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>45107</v>
+        <v>45473</v>
       </c>
       <c r="C5" s="0" t="n">
         <f aca="false">H4</f>
-        <v>42000000</v>
+        <v>13220400</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>8400000</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0</v>
+        <v>241200</v>
       </c>
       <c r="F5" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B5),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>6.85</v>
+        <f aca="false">VLOOKUP(YEAR(B5),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>7.9</v>
       </c>
       <c r="G5" s="0" t="n">
         <f aca="false">ROUND(C5*F5/100/2,2)</f>
-        <v>1438500</v>
+        <v>522205.8</v>
       </c>
       <c r="H5" s="0" t="n">
         <f aca="false">C5+D5-E5</f>
-        <v>50400000</v>
+        <v>12979200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -871,29 +838,29 @@
         <v>32</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">H5</f>
-        <v>50400000</v>
+        <v>12979200</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0</v>
+        <v>275500</v>
       </c>
       <c r="F6" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B6),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>6.85</v>
+        <f aca="false">VLOOKUP(YEAR(B6),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>7.9</v>
       </c>
       <c r="G6" s="0" t="n">
         <f aca="false">ROUND(C6*F6/100/2,2)</f>
-        <v>1726200</v>
+        <v>512678.4</v>
       </c>
       <c r="H6" s="0" t="n">
         <f aca="false">C6+D6-E6</f>
-        <v>50400000</v>
+        <v>12703700</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -901,29 +868,29 @@
         <v>33</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>45473</v>
+        <v>45838</v>
       </c>
       <c r="C7" s="0" t="n">
         <f aca="false">H6</f>
-        <v>50400000</v>
+        <v>12703700</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>1000000</v>
+        <v>309700</v>
       </c>
       <c r="F7" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B7),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>6.75</v>
+        <f aca="false">VLOOKUP(YEAR(B7),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>7.2</v>
       </c>
       <c r="G7" s="0" t="n">
         <f aca="false">ROUND(C7*F7/100/2,2)</f>
-        <v>1701000</v>
+        <v>457333.2</v>
       </c>
       <c r="H7" s="0" t="n">
         <f aca="false">C7+D7-E7</f>
-        <v>49400000</v>
+        <v>12394000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -931,29 +898,29 @@
         <v>34</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>45657</v>
+        <v>46022</v>
       </c>
       <c r="C8" s="0" t="n">
         <f aca="false">H7</f>
-        <v>49400000</v>
+        <v>12394000</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>1100000</v>
+        <v>344000</v>
       </c>
       <c r="F8" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B8),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>6.75</v>
+        <f aca="false">VLOOKUP(YEAR(B8),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>7.2</v>
       </c>
       <c r="G8" s="0" t="n">
         <f aca="false">ROUND(C8*F8/100/2,2)</f>
-        <v>1667250</v>
+        <v>446184</v>
       </c>
       <c r="H8" s="0" t="n">
         <f aca="false">C8+D8-E8</f>
-        <v>48300000</v>
+        <v>12050000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -961,29 +928,29 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>45838</v>
+        <v>46203</v>
       </c>
       <c r="C9" s="0" t="n">
         <f aca="false">H8</f>
-        <v>48300000</v>
+        <v>12050000</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>1300000</v>
+        <v>378200</v>
       </c>
       <c r="F9" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B9),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.65</v>
+        <f aca="false">VLOOKUP(YEAR(B9),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>6.5</v>
       </c>
       <c r="G9" s="0" t="n">
         <f aca="false">ROUND(C9*F9/100/2,2)</f>
-        <v>1364475</v>
+        <v>391625</v>
       </c>
       <c r="H9" s="0" t="n">
         <f aca="false">C9+D9-E9</f>
-        <v>47000000</v>
+        <v>11671800</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -991,29 +958,29 @@
         <v>36</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">H9</f>
-        <v>47000000</v>
+        <v>11671800</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>1400000</v>
+        <v>412500</v>
       </c>
       <c r="F10" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B10),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.65</v>
+        <f aca="false">VLOOKUP(YEAR(B10),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>6.5</v>
       </c>
       <c r="G10" s="0" t="n">
         <f aca="false">ROUND(C10*F10/100/2,2)</f>
-        <v>1327750</v>
+        <v>379333.5</v>
       </c>
       <c r="H10" s="0" t="n">
         <f aca="false">C10+D10-E10</f>
-        <v>45600000</v>
+        <v>11259300</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1021,29 +988,29 @@
         <v>37</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46203</v>
+        <v>46568</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">H10</f>
-        <v>45600000</v>
+        <v>11259300</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>1500000</v>
+        <v>446800</v>
       </c>
       <c r="F11" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B11),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.35</v>
+        <f aca="false">VLOOKUP(YEAR(B11),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>6.1</v>
       </c>
       <c r="G11" s="0" t="n">
         <f aca="false">ROUND(C11*F11/100/2,2)</f>
-        <v>1219800</v>
+        <v>343408.65</v>
       </c>
       <c r="H11" s="0" t="n">
         <f aca="false">C11+D11-E11</f>
-        <v>44100000</v>
+        <v>10812500</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1051,29 +1018,29 @@
         <v>38</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="C12" s="0" t="n">
         <f aca="false">H11</f>
-        <v>44100000</v>
+        <v>10812500</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>1600000</v>
+        <v>481000</v>
       </c>
       <c r="F12" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B12),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.35</v>
+        <f aca="false">VLOOKUP(YEAR(B12),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>6.1</v>
       </c>
       <c r="G12" s="0" t="n">
         <f aca="false">ROUND(C12*F12/100/2,2)</f>
-        <v>1179675</v>
+        <v>329781.25</v>
       </c>
       <c r="H12" s="0" t="n">
         <f aca="false">C12+D12-E12</f>
-        <v>42500000</v>
+        <v>10331500</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1081,29 +1048,29 @@
         <v>39</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46568</v>
+        <v>46934</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">H12</f>
-        <v>42500000</v>
+        <v>10331500</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>1700000</v>
+        <v>515300</v>
       </c>
       <c r="F13" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B13),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B13),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G13" s="0" t="n">
         <f aca="false">ROUND(C13*F13/100/2,2)</f>
-        <v>1115625</v>
+        <v>304779.25</v>
       </c>
       <c r="H13" s="0" t="n">
         <f aca="false">C13+D13-E13</f>
-        <v>40800000</v>
+        <v>9816200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1111,29 +1078,29 @@
         <v>40</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="C14" s="0" t="n">
         <f aca="false">H13</f>
-        <v>40800000</v>
+        <v>9816200</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>1800000</v>
+        <v>549500</v>
       </c>
       <c r="F14" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B14),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B14),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G14" s="0" t="n">
         <f aca="false">ROUND(C14*F14/100/2,2)</f>
-        <v>1071000</v>
+        <v>289577.9</v>
       </c>
       <c r="H14" s="0" t="n">
         <f aca="false">C14+D14-E14</f>
-        <v>39000000</v>
+        <v>9266700</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1141,29 +1108,29 @@
         <v>41</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46934</v>
+        <v>47299</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">H14</f>
-        <v>39000000</v>
+        <v>9266700</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>1900000</v>
+        <v>583800</v>
       </c>
       <c r="F15" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B15),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B15),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G15" s="0" t="n">
         <f aca="false">ROUND(C15*F15/100/2,2)</f>
-        <v>1023750</v>
+        <v>273367.65</v>
       </c>
       <c r="H15" s="0" t="n">
         <f aca="false">C15+D15-E15</f>
-        <v>37100000</v>
+        <v>8682900</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1171,29 +1138,29 @@
         <v>42</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">H15</f>
-        <v>37100000</v>
+        <v>8682900</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>2000000</v>
+        <v>618100</v>
       </c>
       <c r="F16" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B16),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B16),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G16" s="0" t="n">
         <f aca="false">ROUND(C16*F16/100/2,2)</f>
-        <v>973875</v>
+        <v>256145.55</v>
       </c>
       <c r="H16" s="0" t="n">
         <f aca="false">C16+D16-E16</f>
-        <v>35100000</v>
+        <v>8064800</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1201,29 +1168,29 @@
         <v>43</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>47299</v>
+        <v>47664</v>
       </c>
       <c r="C17" s="0" t="n">
         <f aca="false">H16</f>
-        <v>35100000</v>
+        <v>8064800</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>2100000</v>
+        <v>652300</v>
       </c>
       <c r="F17" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B17),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B17),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G17" s="0" t="n">
         <f aca="false">ROUND(C17*F17/100/2,2)</f>
-        <v>921375</v>
+        <v>237911.6</v>
       </c>
       <c r="H17" s="0" t="n">
         <f aca="false">C17+D17-E17</f>
-        <v>33000000</v>
+        <v>7412500</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1231,29 +1198,29 @@
         <v>44</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="C18" s="0" t="n">
         <f aca="false">H17</f>
-        <v>33000000</v>
+        <v>7412500</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>2200000</v>
+        <v>686600</v>
       </c>
       <c r="F18" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B18),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B18),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G18" s="0" t="n">
         <f aca="false">ROUND(C18*F18/100/2,2)</f>
-        <v>866250</v>
+        <v>218668.75</v>
       </c>
       <c r="H18" s="0" t="n">
         <f aca="false">C18+D18-E18</f>
-        <v>30800000</v>
+        <v>6725900</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1261,29 +1228,29 @@
         <v>45</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>47664</v>
+        <v>48029</v>
       </c>
       <c r="C19" s="0" t="n">
         <f aca="false">H18</f>
-        <v>30800000</v>
+        <v>6725900</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>2300000</v>
+        <v>720800</v>
       </c>
       <c r="F19" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B19),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B19),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G19" s="0" t="n">
         <f aca="false">ROUND(C19*F19/100/2,2)</f>
-        <v>808500</v>
+        <v>198414.05</v>
       </c>
       <c r="H19" s="0" t="n">
         <f aca="false">C19+D19-E19</f>
-        <v>28500000</v>
+        <v>6005100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1291,29 +1258,29 @@
         <v>46</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>47848</v>
+        <v>48213</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">H19</f>
-        <v>28500000</v>
+        <v>6005100</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>2400000</v>
+        <v>755100</v>
       </c>
       <c r="F20" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B20),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B20),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G20" s="0" t="n">
         <f aca="false">ROUND(C20*F20/100/2,2)</f>
-        <v>748125</v>
+        <v>177150.45</v>
       </c>
       <c r="H20" s="0" t="n">
         <f aca="false">C20+D20-E20</f>
-        <v>26100000</v>
+        <v>5250000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1321,29 +1288,29 @@
         <v>47</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>48029</v>
+        <v>48395</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">H20</f>
-        <v>26100000</v>
+        <v>5250000</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>2500000</v>
+        <v>789400</v>
       </c>
       <c r="F21" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B21),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B21),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G21" s="0" t="n">
         <f aca="false">ROUND(C21*F21/100/2,2)</f>
-        <v>685125</v>
+        <v>154875</v>
       </c>
       <c r="H21" s="0" t="n">
         <f aca="false">C21+D21-E21</f>
-        <v>23600000</v>
+        <v>4460600</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1351,29 +1318,29 @@
         <v>48</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>48213</v>
+        <v>48579</v>
       </c>
       <c r="C22" s="0" t="n">
         <f aca="false">H21</f>
-        <v>23600000</v>
+        <v>4460600</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>2600000</v>
+        <v>823600</v>
       </c>
       <c r="F22" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B22),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B22),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G22" s="0" t="n">
         <f aca="false">ROUND(C22*F22/100/2,2)</f>
-        <v>619500</v>
+        <v>131587.7</v>
       </c>
       <c r="H22" s="0" t="n">
         <f aca="false">C22+D22-E22</f>
-        <v>21000000</v>
+        <v>3637000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1381,29 +1348,29 @@
         <v>49</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>48395</v>
+        <v>48760</v>
       </c>
       <c r="C23" s="0" t="n">
         <f aca="false">H22</f>
-        <v>21000000</v>
+        <v>3637000</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>2700000</v>
+        <v>857900</v>
       </c>
       <c r="F23" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B23),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B23),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G23" s="0" t="n">
         <f aca="false">ROUND(C23*F23/100/2,2)</f>
-        <v>551250</v>
+        <v>107291.5</v>
       </c>
       <c r="H23" s="0" t="n">
         <f aca="false">C23+D23-E23</f>
-        <v>18300000</v>
+        <v>2779100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1411,29 +1378,29 @@
         <v>50</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>48579</v>
+        <v>48944</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">H23</f>
-        <v>18300000</v>
+        <v>2779100</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>2800000</v>
+        <v>892100</v>
       </c>
       <c r="F24" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B24),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B24),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G24" s="0" t="n">
         <f aca="false">ROUND(C24*F24/100/2,2)</f>
-        <v>480375</v>
+        <v>81983.45</v>
       </c>
       <c r="H24" s="0" t="n">
         <f aca="false">C24+D24-E24</f>
-        <v>15500000</v>
+        <v>1887000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1441,29 +1408,29 @@
         <v>51</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>48760</v>
+        <v>49125</v>
       </c>
       <c r="C25" s="0" t="n">
         <f aca="false">H24</f>
-        <v>15500000</v>
+        <v>1887000</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>2900000</v>
+        <v>926400</v>
       </c>
       <c r="F25" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B25),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B25),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G25" s="0" t="n">
         <f aca="false">ROUND(C25*F25/100/2,2)</f>
-        <v>406875</v>
+        <v>55666.5</v>
       </c>
       <c r="H25" s="0" t="n">
         <f aca="false">C25+D25-E25</f>
-        <v>12600000</v>
+        <v>960600</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1471,118 +1438,28 @@
         <v>52</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>48944</v>
+        <v>49309</v>
       </c>
       <c r="C26" s="0" t="n">
         <f aca="false">H25</f>
-        <v>12600000</v>
+        <v>960600</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>3000000</v>
+        <v>960600</v>
       </c>
       <c r="F26" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B26),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
+        <f aca="false">VLOOKUP(YEAR(B26),Inputs!$A$18:$B$31,2,FALSE())+Inputs_Margin</f>
+        <v>5.9</v>
       </c>
       <c r="G26" s="0" t="n">
         <f aca="false">ROUND(C26*F26/100/2,2)</f>
-        <v>330750</v>
+        <v>28337.7</v>
       </c>
       <c r="H26" s="0" t="n">
         <f aca="false">C26+D26-E26</f>
-        <v>9600000</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>49125</v>
-      </c>
-      <c r="C27" s="0" t="n">
-        <f aca="false">H26</f>
-        <v>9600000</v>
-      </c>
-      <c r="D27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="0" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="F27" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B27),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
-      </c>
-      <c r="G27" s="0" t="n">
-        <f aca="false">ROUND(C27*F27/100/2,2)</f>
-        <v>252000</v>
-      </c>
-      <c r="H27" s="0" t="n">
-        <f aca="false">C27+D27-E27</f>
-        <v>6500000</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>49309</v>
-      </c>
-      <c r="C28" s="0" t="n">
-        <f aca="false">H27</f>
-        <v>6500000</v>
-      </c>
-      <c r="D28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="0" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="F28" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B28),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
-      </c>
-      <c r="G28" s="0" t="n">
-        <f aca="false">ROUND(C28*F28/100/2,2)</f>
-        <v>170625</v>
-      </c>
-      <c r="H28" s="0" t="n">
-        <f aca="false">C28+D28-E28</f>
-        <v>3300000</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>49490</v>
-      </c>
-      <c r="C29" s="0" t="n">
-        <f aca="false">H28</f>
-        <v>3300000</v>
-      </c>
-      <c r="D29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="0" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="F29" s="0" t="n">
-        <f aca="false">VLOOKUP(YEAR(B29),Inputs!$A$18:$B$32,2,FALSE())+Inputs_Margin</f>
-        <v>5.25</v>
-      </c>
-      <c r="G29" s="0" t="n">
-        <f aca="false">ROUND(C29*F29/100/2,2)</f>
-        <v>86625</v>
-      </c>
-      <c r="H29" s="0" t="n">
-        <f aca="false">C29+D29-E29</f>
         <v>0</v>
       </c>
     </row>
@@ -1610,46 +1487,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>1225600</v>
+        <v>513900</v>
       </c>
       <c r="E2" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C2,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C2,Debt!$A$2:$A$29,0)))/2</f>
-        <v>863100</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C2,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C2,Debt!$A$2:$A$26,0)))/2</f>
+        <v>361925.525</v>
       </c>
       <c r="F2" s="0" t="n">
         <f aca="false">ROUND(D2/E2,2)</f>
@@ -1666,20 +1543,20 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>1863700</v>
+        <v>526800</v>
       </c>
       <c r="E3" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C3,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C3,Debt!$A$2:$A$29,0)))/2</f>
-        <v>1350500</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C3,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C3,Debt!$A$2:$A$26,0)))/2</f>
+        <v>381702.9</v>
       </c>
       <c r="F3" s="0" t="n">
         <f aca="false">ROUND(D3/E3,2)</f>
@@ -1696,20 +1573,20 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>1769200</v>
+        <v>500000</v>
       </c>
       <c r="E4" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C4,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C4,Debt!$A$2:$A$29,0)))/2</f>
-        <v>1350500</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C4,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C4,Debt!$A$2:$A$26,0)))/2</f>
+        <v>381702.9</v>
       </c>
       <c r="F4" s="0" t="n">
         <f aca="false">ROUND(D4/E4,2)</f>
@@ -1726,20 +1603,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1757200</v>
+        <v>500500</v>
       </c>
       <c r="E5" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C5,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C5,Debt!$A$2:$A$29,0)))/2</f>
-        <v>1383625</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C5,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C5,Debt!$A$2:$A$26,0)))/2</f>
+        <v>394089.2</v>
       </c>
       <c r="F5" s="0" t="n">
         <f aca="false">ROUND(D5/E5,2)</f>
@@ -1756,20 +1633,20 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1715700</v>
+        <v>488700</v>
       </c>
       <c r="E6" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C6,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C6,Debt!$A$2:$A$29,0)))/2</f>
-        <v>1383625</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C6,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C6,Debt!$A$2:$A$26,0)))/2</f>
+        <v>394089.2</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">ROUND(D6/E6,2)</f>
@@ -1786,20 +1663,20 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1638700</v>
+        <v>471700</v>
       </c>
       <c r="E7" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C7,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C7,Debt!$A$2:$A$29,0)))/2</f>
-        <v>1332237.5</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C7,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C7,Debt!$A$2:$A$26,0)))/2</f>
+        <v>383516.6</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">ROUND(D7/E7,2)</f>
@@ -1816,20 +1693,20 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>1718600</v>
+        <v>494700</v>
       </c>
       <c r="E8" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C8,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C8,Debt!$A$2:$A$29,0)))/2</f>
-        <v>1332237.5</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C8,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C8,Debt!$A$2:$A$26,0)))/2</f>
+        <v>383516.6</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">ROUND(D8/E8,2)</f>
@@ -1846,20 +1723,20 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>1814000</v>
+        <v>525500</v>
       </c>
       <c r="E9" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C9,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C9,Debt!$A$2:$A$29,0)))/2</f>
-        <v>1363875</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C9,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C9,Debt!$A$2:$A$26,0)))/2</f>
+        <v>395092</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">ROUND(D9/E9,2)</f>
@@ -1876,20 +1753,20 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>1854900</v>
+        <v>537300</v>
       </c>
       <c r="E10" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C10,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C10,Debt!$A$2:$A$29,0)))/2</f>
-        <v>1363875</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C10,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C10,Debt!$A$2:$A$26,0)))/2</f>
+        <v>395092</v>
       </c>
       <c r="F10" s="0" t="n">
         <f aca="false">ROUND(D10/E10,2)</f>
@@ -1906,20 +1783,20 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>1822300</v>
+        <v>515800</v>
       </c>
       <c r="E11" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C11,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C11,Debt!$A$2:$A$29,0)))/2</f>
-        <v>1359900</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C11,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C11,Debt!$A$2:$A$26,0)))/2</f>
+        <v>384912.5</v>
       </c>
       <c r="F11" s="0" t="n">
         <f aca="false">ROUND(D11/E11,2)</f>
@@ -1936,20 +1813,20 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>1863100</v>
+        <v>527300</v>
       </c>
       <c r="E12" s="0" t="n">
-        <f aca="false">(INDEX(Debt!$E$2:$E$29,MATCH(C12,Debt!$A$2:$A$29,0))+INDEX(Debt!$G$2:$G$29,MATCH(C12,Debt!$A$2:$A$29,0)))/2</f>
-        <v>1359900</v>
+        <f aca="false">(INDEX(Debt!$E$2:$E$26,MATCH(C12,Debt!$A$2:$A$26,0))+INDEX(Debt!$G$2:$G$26,MATCH(C12,Debt!$A$2:$A$26,0)))/2</f>
+        <v>384912.5</v>
       </c>
       <c r="F12" s="0" t="n">
         <f aca="false">ROUND(D12/E12,2)</f>
@@ -1988,250 +1865,250 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="C1" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B2" s="0" t="n">
         <f aca="false">DSCR!D2</f>
-        <v>1225600</v>
+        <v>513900</v>
       </c>
       <c r="C2" s="0" t="n">
         <f aca="false">DSCR!E2</f>
-        <v>863100</v>
+        <v>361925.525</v>
       </c>
       <c r="D2" s="0" t="n">
         <f aca="false">B2-C2</f>
-        <v>362500</v>
+        <v>151974.475</v>
       </c>
       <c r="E2" s="0" t="n">
         <f aca="false">D2</f>
-        <v>362500</v>
+        <v>151974.475</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">DSCR!D3</f>
-        <v>1863700</v>
+        <v>526800</v>
       </c>
       <c r="C3" s="0" t="n">
         <f aca="false">DSCR!E3</f>
-        <v>1350500</v>
+        <v>381702.9</v>
       </c>
       <c r="D3" s="0" t="n">
         <f aca="false">B3-C3</f>
-        <v>513200</v>
+        <v>145097.1</v>
       </c>
       <c r="E3" s="0" t="n">
         <f aca="false">E2+D3</f>
-        <v>875700</v>
+        <v>297071.575</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B4" s="0" t="n">
         <f aca="false">DSCR!D4</f>
-        <v>1769200</v>
+        <v>500000</v>
       </c>
       <c r="C4" s="0" t="n">
         <f aca="false">DSCR!E4</f>
-        <v>1350500</v>
+        <v>381702.9</v>
       </c>
       <c r="D4" s="0" t="n">
         <f aca="false">B4-C4</f>
-        <v>418700</v>
+        <v>118297.1</v>
       </c>
       <c r="E4" s="0" t="n">
         <f aca="false">E3+D4</f>
-        <v>1294400</v>
+        <v>415368.675</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">DSCR!D5</f>
-        <v>1757200</v>
+        <v>500500</v>
       </c>
       <c r="C5" s="0" t="n">
         <f aca="false">DSCR!E5</f>
-        <v>1383625</v>
+        <v>394089.2</v>
       </c>
       <c r="D5" s="0" t="n">
         <f aca="false">B5-C5</f>
-        <v>373575</v>
+        <v>106410.8</v>
       </c>
       <c r="E5" s="0" t="n">
         <f aca="false">E4+D5</f>
-        <v>1667975</v>
+        <v>521779.475</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">DSCR!D6</f>
-        <v>1715700</v>
+        <v>488700</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">DSCR!E6</f>
-        <v>1383625</v>
+        <v>394089.2</v>
       </c>
       <c r="D6" s="0" t="n">
         <f aca="false">B6-C6</f>
-        <v>332075</v>
+        <v>94610.8</v>
       </c>
       <c r="E6" s="0" t="n">
         <f aca="false">E5+D6</f>
-        <v>2000050</v>
+        <v>616390.275</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">DSCR!D7</f>
-        <v>1638700</v>
+        <v>471700</v>
       </c>
       <c r="C7" s="0" t="n">
         <f aca="false">DSCR!E7</f>
-        <v>1332237.5</v>
+        <v>383516.6</v>
       </c>
       <c r="D7" s="0" t="n">
         <f aca="false">B7-C7</f>
-        <v>306462.5</v>
+        <v>88183.4</v>
       </c>
       <c r="E7" s="0" t="n">
         <f aca="false">E6+D7</f>
-        <v>2306512.5</v>
+        <v>704573.675</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">DSCR!D8</f>
-        <v>1718600</v>
+        <v>494700</v>
       </c>
       <c r="C8" s="0" t="n">
         <f aca="false">DSCR!E8</f>
-        <v>1332237.5</v>
+        <v>383516.6</v>
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">B8-C8</f>
-        <v>386362.5</v>
+        <v>111183.4</v>
       </c>
       <c r="E8" s="0" t="n">
         <f aca="false">E7+D8</f>
-        <v>2692875</v>
+        <v>815757.075</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">DSCR!D9</f>
-        <v>1814000</v>
+        <v>525500</v>
       </c>
       <c r="C9" s="0" t="n">
         <f aca="false">DSCR!E9</f>
-        <v>1363875</v>
+        <v>395092</v>
       </c>
       <c r="D9" s="0" t="n">
         <f aca="false">B9-C9</f>
-        <v>450125</v>
+        <v>130408</v>
       </c>
       <c r="E9" s="0" t="n">
         <f aca="false">E8+D9</f>
-        <v>3143000</v>
+        <v>946165.075</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">DSCR!D10</f>
-        <v>1854900</v>
+        <v>537300</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">DSCR!E10</f>
-        <v>1363875</v>
+        <v>395092</v>
       </c>
       <c r="D10" s="0" t="n">
         <f aca="false">B10-C10</f>
-        <v>491025</v>
+        <v>142208</v>
       </c>
       <c r="E10" s="0" t="n">
         <f aca="false">E9+D10</f>
-        <v>3634025</v>
+        <v>1088373.075</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">DSCR!D11</f>
-        <v>1822300</v>
+        <v>515800</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">DSCR!E11</f>
-        <v>1359900</v>
+        <v>384912.5</v>
       </c>
       <c r="D11" s="0" t="n">
         <f aca="false">B11-C11</f>
-        <v>462400</v>
+        <v>130887.5</v>
       </c>
       <c r="E11" s="0" t="n">
         <f aca="false">E10+D11</f>
-        <v>4096425</v>
+        <v>1219260.575</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">DSCR!D12</f>
-        <v>1863100</v>
+        <v>527300</v>
       </c>
       <c r="C12" s="0" t="n">
         <f aca="false">DSCR!E12</f>
-        <v>1359900</v>
+        <v>384912.5</v>
       </c>
       <c r="D12" s="0" t="n">
         <f aca="false">B12-C12</f>
-        <v>503200</v>
+        <v>142387.5</v>
       </c>
       <c r="E12" s="0" t="n">
         <f aca="false">E11+D12</f>
-        <v>4599625</v>
+        <v>1361648.075</v>
       </c>
     </row>
   </sheetData>
@@ -2255,20 +2132,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
@@ -2276,10 +2153,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/seed_data/excel/Financial_Model_2026.xlsx
+++ b/seed_data/excel/Financial_Model_2026.xlsx
@@ -272,7 +272,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-09T22:07:38+00:00</t>
+    <t xml:space="preserve">2026-10-10T10:25:41+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">demo_today</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-15</t>
+    <t xml:space="preserve">2026-10-06</t>
   </si>
 </sst>
 </file>
@@ -495,7 +495,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46280</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/seed_data/excel/Financial_Model_2026.xlsx
+++ b/seed_data/excel/Financial_Model_2026.xlsx
@@ -272,7 +272,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T10:25:41+00:00</t>
+    <t xml:space="preserve">2026-10-10T16:24:22+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Financial_Model_2026.xlsx
+++ b/seed_data/excel/Financial_Model_2026.xlsx
@@ -272,7 +272,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T16:24:22+00:00</t>
+    <t xml:space="preserve">2026-10-10T18:49:07+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Financial_Model_2026.xlsx
+++ b/seed_data/excel/Financial_Model_2026.xlsx
@@ -272,7 +272,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T18:49:07+00:00</t>
+    <t xml:space="preserve">2026-10-10T19:37:43+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Financial_Model_2026.xlsx
+++ b/seed_data/excel/Financial_Model_2026.xlsx
@@ -272,7 +272,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T19:37:43+00:00</t>
+    <t xml:space="preserve">2026-10-10T20:12:49+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Financial_Model_2026.xlsx
+++ b/seed_data/excel/Financial_Model_2026.xlsx
@@ -272,7 +272,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T20:12:49+00:00</t>
+    <t xml:space="preserve">2026-10-11T07:14:19+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Financial_Model_2026.xlsx
+++ b/seed_data/excel/Financial_Model_2026.xlsx
@@ -272,7 +272,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T07:14:19+00:00</t>
+    <t xml:space="preserve">2026-10-11T18:22:15+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -487,7 +487,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44525</v>
+        <v>44750</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/seed_data/excel/Financial_Model_2026.xlsx
+++ b/seed_data/excel/Financial_Model_2026.xlsx
@@ -272,7 +272,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T18:22:15+00:00</t>
+    <t xml:space="preserve">2026-10-12T13:12:20+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
